--- a/data/experiencia_glocal_catálogo_web_histórico_hasta_10_Agosto_2026.xlsx
+++ b/data/experiencia_glocal_catálogo_web_histórico_hasta_10_Agosto_2026.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV275"/>
+  <dimension ref="A1:AW275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,6 +660,11 @@
       <c r="AV1" t="inlineStr">
         <is>
           <t>es_duplicado_secundario</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>tipo_informacion</t>
         </is>
       </c>
     </row>
@@ -858,6 +863,11 @@
       <c r="AV2" t="b">
         <v>0</v>
       </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1053,6 +1063,11 @@
       </c>
       <c r="AV3" t="b">
         <v>0</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Presentación de publicación o recurso</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1232,6 +1247,11 @@
       <c r="AV4" t="b">
         <v>0</v>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1420,6 +1440,11 @@
       <c r="AV5" t="b">
         <v>0</v>
       </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anuncio o convocatoria</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1606,6 +1631,11 @@
       <c r="AV6" t="b">
         <v>0</v>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1784,6 +1814,11 @@
       <c r="AV7" t="b">
         <v>0</v>
       </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1981,6 +2016,11 @@
       </c>
       <c r="AV8" t="b">
         <v>0</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2178,6 +2218,11 @@
       <c r="AV9" t="b">
         <v>0</v>
       </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2368,6 +2413,11 @@
       <c r="AV10" t="b">
         <v>0</v>
       </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2566,6 +2616,11 @@
       <c r="AV11" t="b">
         <v>0</v>
       </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2756,6 +2811,11 @@
       <c r="AV12" t="b">
         <v>0</v>
       </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2949,6 +3009,11 @@
       </c>
       <c r="AV13" t="b">
         <v>0</v>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -3132,6 +3197,11 @@
       <c r="AV14" t="b">
         <v>0</v>
       </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3314,6 +3384,11 @@
       <c r="AV15" t="b">
         <v>0</v>
       </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3500,6 +3575,11 @@
       <c r="AV16" t="b">
         <v>0</v>
       </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3686,6 +3766,11 @@
       <c r="AV17" t="b">
         <v>0</v>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3879,6 +3964,11 @@
       </c>
       <c r="AV18" t="b">
         <v>0</v>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -4058,6 +4148,11 @@
       <c r="AV19" t="b">
         <v>0</v>
       </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4252,6 +4347,11 @@
       <c r="AV20" t="b">
         <v>0</v>
       </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4434,6 +4534,11 @@
       <c r="AV21" t="b">
         <v>0</v>
       </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4627,6 +4732,11 @@
       </c>
       <c r="AV22" t="b">
         <v>0</v>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -4813,6 +4923,11 @@
       </c>
       <c r="AV23" t="b">
         <v>0</v>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -5004,6 +5119,11 @@
       <c r="AV24" t="b">
         <v>0</v>
       </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5190,6 +5310,11 @@
       <c r="AV25" t="b">
         <v>0</v>
       </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5379,6 +5504,11 @@
       </c>
       <c r="AV26" t="b">
         <v>0</v>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -5562,6 +5692,11 @@
       <c r="AV27" t="b">
         <v>0</v>
       </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5744,6 +5879,11 @@
       <c r="AV28" t="b">
         <v>0</v>
       </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5933,6 +6073,11 @@
       </c>
       <c r="AV29" t="b">
         <v>0</v>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -6092,6 +6237,11 @@
       <c r="AV30" t="b">
         <v>0</v>
       </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6286,6 +6436,11 @@
       <c r="AV31" t="b">
         <v>0</v>
       </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6471,6 +6626,11 @@
       </c>
       <c r="AV32" t="b">
         <v>0</v>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -6654,6 +6814,11 @@
       <c r="AV33" t="b">
         <v>0</v>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6836,6 +7001,11 @@
       <c r="AV34" t="b">
         <v>0</v>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7025,6 +7195,11 @@
       </c>
       <c r="AV35" t="b">
         <v>0</v>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -7212,6 +7387,11 @@
       <c r="AV36" t="b">
         <v>0</v>
       </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7398,6 +7578,11 @@
       <c r="AV37" t="b">
         <v>0</v>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7588,6 +7773,11 @@
       <c r="AV38" t="b">
         <v>0</v>
       </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7773,6 +7963,11 @@
       </c>
       <c r="AV39" t="b">
         <v>0</v>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -7956,6 +8151,11 @@
       <c r="AV40" t="b">
         <v>0</v>
       </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anuncio o convocatoria</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8142,6 +8342,11 @@
       <c r="AV41" t="b">
         <v>0</v>
       </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8327,6 +8532,11 @@
       </c>
       <c r="AV42" t="b">
         <v>0</v>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -8510,6 +8720,11 @@
       <c r="AV43" t="b">
         <v>0</v>
       </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8704,6 +8919,11 @@
       <c r="AV44" t="b">
         <v>0</v>
       </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8881,6 +9101,11 @@
       </c>
       <c r="AV45" t="b">
         <v>0</v>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -9063,6 +9288,11 @@
       </c>
       <c r="AV46" t="b">
         <v>0</v>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -9246,6 +9476,11 @@
       <c r="AV47" t="b">
         <v>0</v>
       </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9416,6 +9651,11 @@
       <c r="AV48" t="b">
         <v>0</v>
       </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9601,6 +9841,11 @@
       </c>
       <c r="AV49" t="b">
         <v>0</v>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -9788,6 +10033,11 @@
       <c r="AV50" t="b">
         <v>0</v>
       </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9973,6 +10223,11 @@
       </c>
       <c r="AV51" t="b">
         <v>0</v>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -10156,6 +10411,11 @@
       <c r="AV52" t="b">
         <v>0</v>
       </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10350,6 +10610,11 @@
       <c r="AV53" t="b">
         <v>0</v>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10539,6 +10804,11 @@
       </c>
       <c r="AV54" t="b">
         <v>0</v>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -10726,6 +10996,11 @@
       <c r="AV55" t="b">
         <v>0</v>
       </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10912,6 +11187,11 @@
       <c r="AV56" t="b">
         <v>0</v>
       </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -11101,6 +11381,11 @@
       </c>
       <c r="AV57" t="b">
         <v>0</v>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -11264,6 +11549,11 @@
       <c r="AV58" t="b">
         <v>0</v>
       </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Presentación de publicación o recurso</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -11450,6 +11740,11 @@
       <c r="AV59" t="b">
         <v>0</v>
       </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -11635,6 +11930,11 @@
       </c>
       <c r="AV60" t="b">
         <v>0</v>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -11822,6 +12122,11 @@
       <c r="AV61" t="b">
         <v>0</v>
       </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -12008,6 +12313,11 @@
       <c r="AV62" t="b">
         <v>0</v>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12194,6 +12504,11 @@
       <c r="AV63" t="b">
         <v>0</v>
       </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Presentación de publicación o recurso</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -12364,6 +12679,11 @@
       <c r="AV64" t="b">
         <v>0</v>
       </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -12550,6 +12870,11 @@
       <c r="AV65" t="b">
         <v>0</v>
       </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12736,6 +13061,11 @@
       <c r="AV66" t="b">
         <v>0</v>
       </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -12929,6 +13259,11 @@
       </c>
       <c r="AV67" t="b">
         <v>0</v>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -13112,6 +13447,11 @@
       <c r="AV68" t="b">
         <v>0</v>
       </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13303,6 +13643,11 @@
       </c>
       <c r="AV69" t="b">
         <v>0</v>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -13489,6 +13834,11 @@
       </c>
       <c r="AV70" t="b">
         <v>0</v>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -13652,6 +14002,11 @@
       <c r="AV71" t="b">
         <v>0</v>
       </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13838,6 +14193,11 @@
       <c r="AV72" t="b">
         <v>0</v>
       </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -14023,6 +14383,11 @@
       </c>
       <c r="AV73" t="b">
         <v>0</v>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -14202,6 +14567,11 @@
       <c r="AV74" t="b">
         <v>0</v>
       </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -14384,6 +14754,11 @@
       <c r="AV75" t="b">
         <v>0</v>
       </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14553,6 +14928,11 @@
       </c>
       <c r="AV76" t="b">
         <v>0</v>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -14736,6 +15116,11 @@
       <c r="AV77" t="b">
         <v>0</v>
       </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -14914,6 +15299,11 @@
       <c r="AV78" t="b">
         <v>0</v>
       </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -15096,6 +15486,11 @@
       <c r="AV79" t="b">
         <v>0</v>
       </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -15282,6 +15677,11 @@
       <c r="AV80" t="b">
         <v>0</v>
       </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -15448,6 +15848,11 @@
       <c r="AV81" t="b">
         <v>0</v>
       </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -15637,6 +16042,11 @@
       </c>
       <c r="AV82" t="b">
         <v>0</v>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -15820,6 +16230,11 @@
       <c r="AV83" t="b">
         <v>0</v>
       </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -16006,6 +16421,11 @@
       <c r="AV84" t="b">
         <v>0</v>
       </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16188,6 +16608,11 @@
       <c r="AV85" t="b">
         <v>0</v>
       </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16373,6 +16798,11 @@
       </c>
       <c r="AV86" t="b">
         <v>0</v>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anuncio o convocatoria</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -16555,6 +16985,11 @@
       </c>
       <c r="AV87" t="b">
         <v>0</v>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -16718,6 +17153,11 @@
       <c r="AV88" t="b">
         <v>0</v>
       </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -16900,6 +17340,11 @@
       <c r="AV89" t="b">
         <v>0</v>
       </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -17085,6 +17530,11 @@
       </c>
       <c r="AV90" t="b">
         <v>0</v>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -17268,6 +17718,11 @@
       <c r="AV91" t="b">
         <v>0</v>
       </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -17454,6 +17909,11 @@
       <c r="AV92" t="b">
         <v>0</v>
       </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -17640,6 +18100,11 @@
       <c r="AV93" t="b">
         <v>0</v>
       </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -17826,6 +18291,11 @@
       <c r="AV94" t="b">
         <v>0</v>
       </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -18011,6 +18481,11 @@
       </c>
       <c r="AV95" t="b">
         <v>0</v>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -18190,6 +18665,11 @@
       <c r="AV96" t="b">
         <v>0</v>
       </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -18375,6 +18855,11 @@
       </c>
       <c r="AV97" t="b">
         <v>0</v>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -18558,6 +19043,11 @@
       <c r="AV98" t="b">
         <v>0</v>
       </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -18744,6 +19234,11 @@
       <c r="AV99" t="b">
         <v>0</v>
       </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -18930,6 +19425,11 @@
       <c r="AV100" t="b">
         <v>0</v>
       </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19116,6 +19616,11 @@
       <c r="AV101" t="b">
         <v>0</v>
       </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19310,6 +19815,11 @@
       <c r="AV102" t="b">
         <v>0</v>
       </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19500,6 +20010,11 @@
       <c r="AV103" t="b">
         <v>0</v>
       </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19689,6 +20204,11 @@
       </c>
       <c r="AV104" t="b">
         <v>0</v>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -19868,6 +20388,11 @@
       <c r="AV105" t="b">
         <v>0</v>
       </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -20054,6 +20579,11 @@
       <c r="AV106" t="b">
         <v>0</v>
       </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -20240,6 +20770,11 @@
       <c r="AV107" t="b">
         <v>0</v>
       </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20410,6 +20945,11 @@
       <c r="AV108" t="b">
         <v>0</v>
       </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Anuncio o convocatoria</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20596,6 +21136,11 @@
       <c r="AV109" t="b">
         <v>0</v>
       </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -20766,6 +21311,11 @@
       <c r="AV110" t="b">
         <v>0</v>
       </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20960,6 +21510,11 @@
       <c r="AV111" t="b">
         <v>0</v>
       </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -21150,6 +21705,11 @@
       <c r="AV112" t="b">
         <v>0</v>
       </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -21343,6 +21903,11 @@
       </c>
       <c r="AV113" t="b">
         <v>0</v>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -21530,6 +22095,11 @@
       <c r="AV114" t="b">
         <v>0</v>
       </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -21720,6 +22290,11 @@
       <c r="AV115" t="b">
         <v>0</v>
       </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -21909,6 +22484,11 @@
       </c>
       <c r="AV116" t="b">
         <v>0</v>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -22096,6 +22676,11 @@
       <c r="AV117" t="b">
         <v>0</v>
       </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -22281,6 +22866,11 @@
       </c>
       <c r="AV118" t="b">
         <v>0</v>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Presentación de publicación o recurso</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -22464,6 +23054,11 @@
       <c r="AV119" t="b">
         <v>0</v>
       </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -22646,6 +23241,11 @@
       <c r="AV120" t="b">
         <v>0</v>
       </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -22831,6 +23431,11 @@
       </c>
       <c r="AV121" t="b">
         <v>0</v>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -23014,6 +23619,11 @@
       <c r="AV122" t="b">
         <v>0</v>
       </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -23203,6 +23813,11 @@
       </c>
       <c r="AV123" t="b">
         <v>0</v>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -23386,6 +24001,11 @@
       <c r="AV124" t="b">
         <v>0</v>
       </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -23576,6 +24196,11 @@
       <c r="AV125" t="b">
         <v>0</v>
       </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -23766,6 +24391,11 @@
       <c r="AV126" t="b">
         <v>0</v>
       </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -23955,6 +24585,11 @@
       </c>
       <c r="AV127" t="b">
         <v>0</v>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -24134,6 +24769,11 @@
       <c r="AV128" t="b">
         <v>0</v>
       </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -24320,6 +24960,11 @@
       <c r="AV129" t="b">
         <v>0</v>
       </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -24510,6 +25155,11 @@
       <c r="AV130" t="b">
         <v>0</v>
       </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -24699,6 +25349,11 @@
       </c>
       <c r="AV131" t="b">
         <v>0</v>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -24885,6 +25540,11 @@
       </c>
       <c r="AV132" t="b">
         <v>0</v>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -25068,6 +25728,11 @@
       <c r="AV133" t="b">
         <v>0</v>
       </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -25230,6 +25895,11 @@
       <c r="AV134" t="b">
         <v>0</v>
       </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -25419,6 +26089,11 @@
       </c>
       <c r="AV135" t="b">
         <v>0</v>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -25598,6 +26273,11 @@
       <c r="AV136" t="b">
         <v>0</v>
       </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -25772,6 +26452,11 @@
       <c r="AV137" t="b">
         <v>0</v>
       </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -25962,6 +26647,11 @@
       <c r="AV138" t="b">
         <v>0</v>
       </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -26151,6 +26841,11 @@
       </c>
       <c r="AV139" t="b">
         <v>0</v>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -26338,6 +27033,11 @@
       <c r="AV140" t="b">
         <v>0</v>
       </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -26528,6 +27228,11 @@
       <c r="AV141" t="b">
         <v>0</v>
       </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Anuncio o convocatoria</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -26717,6 +27422,11 @@
       </c>
       <c r="AV142" t="b">
         <v>0</v>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -26900,6 +27610,11 @@
       <c r="AV143" t="b">
         <v>0</v>
       </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -27065,6 +27780,11 @@
       </c>
       <c r="AV144" t="b">
         <v>0</v>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -27248,6 +27968,11 @@
       <c r="AV145" t="b">
         <v>0</v>
       </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -27445,6 +28170,11 @@
       </c>
       <c r="AV146" t="b">
         <v>0</v>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -27624,6 +28354,11 @@
       <c r="AV147" t="b">
         <v>0</v>
       </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -27806,6 +28541,11 @@
       <c r="AV148" t="b">
         <v>0</v>
       </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -27991,6 +28731,11 @@
       </c>
       <c r="AV149" t="b">
         <v>0</v>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -28174,6 +28919,11 @@
       <c r="AV150" t="b">
         <v>0</v>
       </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -28363,6 +29113,11 @@
       </c>
       <c r="AV151" t="b">
         <v>0</v>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -28546,6 +29301,11 @@
       <c r="AV152" t="b">
         <v>0</v>
       </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -28732,6 +29492,11 @@
       <c r="AV153" t="b">
         <v>0</v>
       </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -28901,6 +29666,11 @@
       </c>
       <c r="AV154" t="b">
         <v>0</v>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -29088,6 +29858,11 @@
       <c r="AV155" t="b">
         <v>0</v>
       </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -29262,6 +30037,11 @@
       <c r="AV156" t="b">
         <v>0</v>
       </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -29448,6 +30228,11 @@
       <c r="AV157" t="b">
         <v>0</v>
       </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -29634,6 +30419,11 @@
       <c r="AV158" t="b">
         <v>0</v>
       </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -29828,6 +30618,11 @@
       <c r="AV159" t="b">
         <v>0</v>
       </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -30022,6 +30817,11 @@
       <c r="AV160" t="b">
         <v>0</v>
       </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -30208,6 +31008,11 @@
       <c r="AV161" t="b">
         <v>0</v>
       </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -30397,6 +31202,11 @@
       </c>
       <c r="AV162" t="b">
         <v>0</v>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -30592,6 +31402,11 @@
       <c r="AV163" t="b">
         <v>0</v>
       </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -30778,6 +31593,11 @@
       <c r="AV164" t="b">
         <v>0</v>
       </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -30967,6 +31787,11 @@
       </c>
       <c r="AV165" t="b">
         <v>0</v>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -31154,6 +31979,11 @@
       <c r="AV166" t="b">
         <v>0</v>
       </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -31340,6 +32170,11 @@
       <c r="AV167" t="b">
         <v>0</v>
       </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -31533,6 +32368,11 @@
       </c>
       <c r="AV168" t="b">
         <v>0</v>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -31700,6 +32540,11 @@
       <c r="AV169" t="b">
         <v>0</v>
       </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -31889,6 +32734,11 @@
       </c>
       <c r="AV170" t="b">
         <v>0</v>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -32075,6 +32925,11 @@
       </c>
       <c r="AV171" t="b">
         <v>0</v>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -32258,6 +33113,11 @@
       <c r="AV172" t="b">
         <v>0</v>
       </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -32444,6 +33304,11 @@
       <c r="AV173" t="b">
         <v>0</v>
       </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -32630,6 +33495,11 @@
       <c r="AV174" t="b">
         <v>0</v>
       </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -32819,6 +33689,11 @@
       </c>
       <c r="AV175" t="b">
         <v>0</v>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -33002,6 +33877,11 @@
       <c r="AV176" t="b">
         <v>0</v>
       </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -33191,6 +34071,11 @@
       </c>
       <c r="AV177" t="b">
         <v>0</v>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -33378,6 +34263,11 @@
       <c r="AV178" t="b">
         <v>0</v>
       </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -33564,6 +34454,11 @@
       <c r="AV179" t="b">
         <v>0</v>
       </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -33749,6 +34644,11 @@
       </c>
       <c r="AV180" t="b">
         <v>0</v>
+      </c>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -33928,6 +34828,11 @@
       <c r="AV181" t="b">
         <v>0</v>
       </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -34090,6 +34995,11 @@
       <c r="AV182" t="b">
         <v>0</v>
       </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -34272,6 +35182,11 @@
       <c r="AV183" t="b">
         <v>0</v>
       </c>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -34461,6 +35376,11 @@
       </c>
       <c r="AV184" t="b">
         <v>0</v>
+      </c>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -34648,6 +35568,11 @@
       <c r="AV185" t="b">
         <v>0</v>
       </c>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -34837,6 +35762,11 @@
       </c>
       <c r="AV186" t="b">
         <v>0</v>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="187">
@@ -35016,6 +35946,11 @@
       <c r="AV187" t="b">
         <v>0</v>
       </c>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -35205,6 +36140,11 @@
       </c>
       <c r="AV188" t="b">
         <v>0</v>
+      </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -35384,6 +36324,11 @@
       <c r="AV189" t="b">
         <v>0</v>
       </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -35570,6 +36515,11 @@
       <c r="AV190" t="b">
         <v>0</v>
       </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -35756,6 +36706,11 @@
       <c r="AV191" t="b">
         <v>0</v>
       </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -35945,6 +36900,11 @@
       </c>
       <c r="AV192" t="b">
         <v>0</v>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -36127,6 +37087,11 @@
       </c>
       <c r="AV193" t="b">
         <v>0</v>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -36306,6 +37271,11 @@
       <c r="AV194" t="b">
         <v>0</v>
       </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -36488,6 +37458,11 @@
       <c r="AV195" t="b">
         <v>0</v>
       </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -36674,6 +37649,11 @@
       <c r="AV196" t="b">
         <v>0</v>
       </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -36859,6 +37839,11 @@
       </c>
       <c r="AV197" t="b">
         <v>0</v>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -37046,6 +38031,11 @@
       <c r="AV198" t="b">
         <v>0</v>
       </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Anuncio o convocatoria</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -37240,6 +38230,11 @@
       <c r="AV199" t="b">
         <v>0</v>
       </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -37425,6 +38420,11 @@
       </c>
       <c r="AV200" t="b">
         <v>0</v>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -37616,6 +38616,11 @@
       <c r="AV201" t="b">
         <v>0</v>
       </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -37794,6 +38799,11 @@
       <c r="AV202" t="b">
         <v>0</v>
       </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -37975,6 +38985,11 @@
       </c>
       <c r="AV203" t="b">
         <v>0</v>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -38158,6 +39173,11 @@
       <c r="AV204" t="b">
         <v>0</v>
       </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -38348,6 +39368,11 @@
       <c r="AV205" t="b">
         <v>0</v>
       </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -38537,6 +39562,11 @@
       </c>
       <c r="AV206" t="b">
         <v>0</v>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -38724,6 +39754,11 @@
       <c r="AV207" t="b">
         <v>0</v>
       </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -38913,6 +39948,11 @@
       </c>
       <c r="AV208" t="b">
         <v>0</v>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -39096,6 +40136,11 @@
       <c r="AV209" t="b">
         <v>0</v>
       </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -39278,6 +40323,11 @@
       <c r="AV210" t="b">
         <v>0</v>
       </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -39463,6 +40513,11 @@
       </c>
       <c r="AV211" t="b">
         <v>0</v>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -39650,6 +40705,11 @@
       <c r="AV212" t="b">
         <v>0</v>
       </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -39836,6 +40896,11 @@
       <c r="AV213" t="b">
         <v>0</v>
       </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -40029,6 +41094,11 @@
       </c>
       <c r="AV214" t="b">
         <v>0</v>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -40212,6 +41282,11 @@
       <c r="AV215" t="b">
         <v>0</v>
       </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -40398,6 +41473,11 @@
       <c r="AV216" t="b">
         <v>0</v>
       </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -40584,6 +41664,11 @@
       <c r="AV217" t="b">
         <v>0</v>
       </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -40781,6 +41866,11 @@
       </c>
       <c r="AV218" t="b">
         <v>0</v>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -40975,6 +42065,11 @@
       </c>
       <c r="AV219" t="b">
         <v>0</v>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -41158,6 +42253,11 @@
       <c r="AV220" t="b">
         <v>0</v>
       </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -41344,6 +42444,11 @@
       <c r="AV221" t="b">
         <v>0</v>
       </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -41533,6 +42638,11 @@
       </c>
       <c r="AV222" t="b">
         <v>0</v>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -41716,6 +42826,11 @@
       <c r="AV223" t="b">
         <v>0</v>
       </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -41901,6 +43016,11 @@
       </c>
       <c r="AV224" t="b">
         <v>0</v>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -42080,6 +43200,11 @@
       <c r="AV225" t="b">
         <v>0</v>
       </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -42262,6 +43387,11 @@
       <c r="AV226" t="b">
         <v>0</v>
       </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -42444,6 +43574,11 @@
       <c r="AV227" t="b">
         <v>0</v>
       </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -42626,6 +43761,11 @@
       <c r="AV228" t="b">
         <v>0</v>
       </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -42811,6 +43951,11 @@
       </c>
       <c r="AV229" t="b">
         <v>0</v>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -42993,6 +44138,11 @@
       </c>
       <c r="AV230" t="b">
         <v>0</v>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -43176,6 +44326,11 @@
       <c r="AV231" t="b">
         <v>0</v>
       </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -43369,6 +44524,11 @@
       </c>
       <c r="AV232" t="b">
         <v>0</v>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -43551,6 +44711,11 @@
       </c>
       <c r="AV233" t="b">
         <v>0</v>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -43734,6 +44899,11 @@
       <c r="AV234" t="b">
         <v>0</v>
       </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -43916,6 +45086,11 @@
       <c r="AV235" t="b">
         <v>0</v>
       </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -44102,6 +45277,11 @@
       <c r="AV236" t="b">
         <v>0</v>
       </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -44287,6 +45467,11 @@
       </c>
       <c r="AV237" t="b">
         <v>0</v>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="238">
@@ -44474,6 +45659,11 @@
       <c r="AV238" t="b">
         <v>0</v>
       </c>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -44659,6 +45849,11 @@
       </c>
       <c r="AV239" t="b">
         <v>0</v>
+      </c>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -44842,6 +46037,11 @@
       <c r="AV240" t="b">
         <v>0</v>
       </c>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -45028,6 +46228,11 @@
       <c r="AV241" t="b">
         <v>0</v>
       </c>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -45210,6 +46415,11 @@
       <c r="AV242" t="b">
         <v>0</v>
       </c>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -45407,6 +46617,11 @@
       </c>
       <c r="AV243" t="b">
         <v>0</v>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -45593,6 +46808,11 @@
       </c>
       <c r="AV244" t="b">
         <v>0</v>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -45776,6 +46996,11 @@
       <c r="AV245" t="b">
         <v>0</v>
       </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -45962,6 +47187,11 @@
       <c r="AV246" t="b">
         <v>0</v>
       </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -46144,6 +47374,11 @@
       <c r="AV247" t="b">
         <v>0</v>
       </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -46329,6 +47564,11 @@
       </c>
       <c r="AV248" t="b">
         <v>0</v>
+      </c>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="249">
@@ -46520,6 +47760,11 @@
       <c r="AV249" t="b">
         <v>0</v>
       </c>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -46706,6 +47951,11 @@
       <c r="AV250" t="b">
         <v>0</v>
       </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -46892,6 +48142,11 @@
       <c r="AV251" t="b">
         <v>0</v>
       </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -47086,6 +48341,11 @@
       <c r="AV252" t="b">
         <v>0</v>
       </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -47272,6 +48532,11 @@
       <c r="AV253" t="b">
         <v>0</v>
       </c>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -47462,6 +48727,11 @@
       <c r="AV254" t="b">
         <v>0</v>
       </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -47651,6 +48921,11 @@
       </c>
       <c r="AV255" t="b">
         <v>0</v>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -47830,6 +49105,11 @@
       <c r="AV256" t="b">
         <v>0</v>
       </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -48016,6 +49296,11 @@
       <c r="AV257" t="b">
         <v>0</v>
       </c>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -48201,6 +49486,11 @@
       </c>
       <c r="AV258" t="b">
         <v>0</v>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -48376,6 +49666,11 @@
       <c r="AV259" t="b">
         <v>0</v>
       </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -48572,6 +49867,11 @@
       <c r="AV260" t="b">
         <v>0</v>
       </c>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Anuncio o convocatoria</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -48788,6 +50088,11 @@
       <c r="AV261" t="b">
         <v>0</v>
       </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Anuncio o convocatoria</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -49004,6 +50309,11 @@
       <c r="AV262" t="b">
         <v>0</v>
       </c>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Anuncio o convocatoria</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -49219,6 +50529,11 @@
       </c>
       <c r="AV263" t="b">
         <v>0</v>
+      </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Reflexión u opinión</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -49416,6 +50731,11 @@
       <c r="AV264" t="b">
         <v>0</v>
       </c>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -49632,6 +50952,11 @@
       <c r="AV265" t="b">
         <v>0</v>
       </c>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -49847,6 +51172,11 @@
       </c>
       <c r="AV266" t="b">
         <v>0</v>
+      </c>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -50044,6 +51374,11 @@
       <c r="AV267" t="b">
         <v>0</v>
       </c>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -50259,6 +51594,11 @@
       </c>
       <c r="AV268" t="b">
         <v>0</v>
+      </c>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>Descripción de programa</t>
+        </is>
       </c>
     </row>
     <row r="269">
@@ -50456,6 +51796,11 @@
       <c r="AV269" t="b">
         <v>0</v>
       </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Descripción de programa</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -50652,6 +51997,11 @@
       <c r="AV270" t="b">
         <v>0</v>
       </c>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Testimonio o entrevista</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -50848,6 +52198,11 @@
       <c r="AV271" t="b">
         <v>0</v>
       </c>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Presentación de publicación o recurso</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -51044,6 +52399,11 @@
       <c r="AV272" t="b">
         <v>0</v>
       </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Presentación de publicación o recurso</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -51260,6 +52620,11 @@
       <c r="AV273" t="b">
         <v>0</v>
       </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -51476,6 +52841,11 @@
       <c r="AV274" t="b">
         <v>0</v>
       </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -51691,6 +53061,11 @@
       </c>
       <c r="AV275" t="b">
         <v>0</v>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -51704,7 +53079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52973,6 +54348,33 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>Generado en el proceso de unificación del catálogo (revisión manual caso a caso)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>tipo_informacion</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Qué clase de contenido es el registro (crónica de una acción ya realizada, anuncio/convocatoria, reflexión u opinión, testimonio o entrevista, presentación de una publicación, o descripción general de un programa).</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Categórica única</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Evidencia de acción realizada / Anuncio o convocatoria / Reflexión u opinión / Testimonio o entrevista / Presentación de publicación o recurso / Descripción de programa</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Clasificación heurística por reglas de palabras clave sobre título/contenido (y categoría WordPress de origen para fundacionglocal.org) — editable a mano si se detecta un caso mal clasificado</t>
         </is>
       </c>
     </row>
